--- a/output/yearly_benthic_cover_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_95_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.60758927408298</v>
+        <v>44.75936562476237</v>
       </c>
       <c r="M2" t="n">
-        <v>98.47041070070978</v>
+        <v>101.5641723294113</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05775740489035</v>
+        <v>88.02864858545945</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92194528435987</v>
+        <v>45.91298220052779</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228813808055597</v>
+        <v>2.228745960498927</v>
       </c>
       <c r="E3" t="n">
-        <v>5.704242205496097</v>
+        <v>5.697513733557122</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429379360185324</v>
+        <v>0.7429153201663089</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97045010982765</v>
+        <v>33.96764732489657</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17514505685249</v>
+        <v>34.1741047276502</v>
       </c>
       <c r="I3" t="n">
-        <v>6.592806188524182</v>
+        <v>6.574500767650891</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643362100115827</v>
+        <v>4.64322075103943</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94224259510964</v>
+        <v>11.97135141454056</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89917301986821</v>
+        <v>48.87967714670805</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7633608993377</v>
+        <v>106.7640107617764</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.19428415577451</v>
+        <v>87.15404464239171</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69863833646593</v>
+        <v>42.67534350266938</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187480709440302</v>
+        <v>2.186799518095307</v>
       </c>
       <c r="E4" t="n">
-        <v>6.51605242605315</v>
+        <v>6.50532534742488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445016071960681</v>
+        <v>0.7444753145504198</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34047197557498</v>
+        <v>33.32835420340449</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24707393101912</v>
+        <v>34.2458644693193</v>
       </c>
       <c r="I4" t="n">
-        <v>5.505568461515471</v>
+        <v>5.490255073657183</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653135044975425</v>
+        <v>4.652970715940123</v>
       </c>
       <c r="K4" t="n">
-        <v>12.80571584422549</v>
+        <v>12.84595535760828</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3125123140718</v>
+        <v>44.29607611839871</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81686649476322</v>
+        <v>99.81737497867638</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.14403447751798</v>
+        <v>86.0044915007514</v>
       </c>
       <c r="C5" t="n">
-        <v>42.50291932632955</v>
+        <v>42.37793666873163</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136631124067884</v>
+        <v>2.130753650662294</v>
       </c>
       <c r="E5" t="n">
-        <v>7.130604246448593</v>
+        <v>7.102489217435981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458256797750996</v>
+        <v>0.7457977972062622</v>
       </c>
       <c r="G5" t="n">
-        <v>32.56544837478972</v>
+        <v>32.47417598268151</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30798126965458</v>
+        <v>34.30669867148805</v>
       </c>
       <c r="I5" t="n">
-        <v>4.596133284187726</v>
+        <v>4.583339948738177</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661410498594372</v>
+        <v>4.661236232539138</v>
       </c>
       <c r="K5" t="n">
-        <v>13.85596552248203</v>
+        <v>13.99550849924859</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4881826939241</v>
+        <v>43.47404774664041</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84706754273569</v>
+        <v>99.84749291462063</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.01177620809133</v>
+        <v>84.6903585239572</v>
       </c>
       <c r="C6" t="n">
-        <v>42.08460300068072</v>
+        <v>41.77565866407213</v>
       </c>
       <c r="D6" t="n">
-        <v>2.081926937654351</v>
+        <v>2.066723972177551</v>
       </c>
       <c r="E6" t="n">
-        <v>7.587351281384239</v>
+        <v>7.526591042221253</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469474426635603</v>
+        <v>0.7469206428552702</v>
       </c>
       <c r="G6" t="n">
-        <v>31.73167489912158</v>
+        <v>31.49831889728744</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35958236252377</v>
+        <v>34.35834957134242</v>
       </c>
       <c r="I6" t="n">
-        <v>3.835871768096578</v>
+        <v>3.825200380227823</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668421516647252</v>
+        <v>4.668254017845438</v>
       </c>
       <c r="K6" t="n">
-        <v>14.98822379190868</v>
+        <v>15.30964147604281</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79950283840539</v>
+        <v>42.787384861309</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87232963099478</v>
+        <v>99.87268500142393</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.58965992091197</v>
+        <v>83.21760686055879</v>
       </c>
       <c r="C7" t="n">
-        <v>41.25854424143557</v>
+        <v>40.89708072173032</v>
       </c>
       <c r="D7" t="n">
-        <v>2.01297902229665</v>
+        <v>1.995198751188205</v>
       </c>
       <c r="E7" t="n">
-        <v>7.869518213950673</v>
+        <v>7.798067696530416</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479007940788943</v>
+        <v>0.7478755602584323</v>
       </c>
       <c r="G7" t="n">
-        <v>30.68080572809885</v>
+        <v>30.40822450139788</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40343652762913</v>
+        <v>34.40227577188787</v>
       </c>
       <c r="I7" t="n">
-        <v>3.200639671864693</v>
+        <v>3.191742327680787</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67437996299309</v>
+        <v>4.674222251615202</v>
       </c>
       <c r="K7" t="n">
-        <v>16.41034007908803</v>
+        <v>16.78239313944121</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22456368591816</v>
+        <v>42.21427057271104</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89344800644176</v>
+        <v>99.89374443388257</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.47183066049303</v>
+        <v>88.20705625071328</v>
       </c>
       <c r="C8" t="n">
-        <v>43.56730714132628</v>
+        <v>43.27744168956789</v>
       </c>
       <c r="D8" t="n">
-        <v>2.017264698572348</v>
+        <v>1.999478703515501</v>
       </c>
       <c r="E8" t="n">
-        <v>9.707474471740746</v>
+        <v>9.685533716579647</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494930911938947</v>
+        <v>0.7494798474216785</v>
       </c>
       <c r="G8" t="n">
-        <v>31.18583062766537</v>
+        <v>30.93578497899414</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47668219491915</v>
+        <v>34.47607298139719</v>
       </c>
       <c r="I8" t="n">
-        <v>5.650753756439669</v>
+        <v>5.676456976419634</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684331819961842</v>
+        <v>4.68424904638549</v>
       </c>
       <c r="K8" t="n">
-        <v>11.52816933950696</v>
+        <v>11.79294374928671</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7165652279234</v>
+        <v>44.74080435025371</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81204170875664</v>
+        <v>99.81118978910831</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.56848768604527</v>
+        <v>86.26759849157881</v>
       </c>
       <c r="C9" t="n">
-        <v>42.5415468253412</v>
+        <v>42.21921628965699</v>
       </c>
       <c r="D9" t="n">
-        <v>1.931288622931603</v>
+        <v>1.911987219332034</v>
       </c>
       <c r="E9" t="n">
-        <v>10.07999322482631</v>
+        <v>10.05156285851228</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508545354356045</v>
+        <v>0.750852250324952</v>
       </c>
       <c r="G9" t="n">
-        <v>29.85668659671041</v>
+        <v>29.58212327835486</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5393086300378</v>
+        <v>34.53920351494777</v>
       </c>
       <c r="I9" t="n">
-        <v>4.717515229631009</v>
+        <v>4.739042805575967</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692840846472528</v>
+        <v>4.692826564530949</v>
       </c>
       <c r="K9" t="n">
-        <v>13.43151231395474</v>
+        <v>13.73240150842119</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86997547858071</v>
+        <v>43.89070284146571</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84303461787665</v>
+        <v>99.84232063954389</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.4055013665933</v>
+        <v>84.1691098295933</v>
       </c>
       <c r="C10" t="n">
-        <v>41.11104710901181</v>
+        <v>40.85623733420192</v>
       </c>
       <c r="D10" t="n">
-        <v>1.834362138931722</v>
+        <v>1.818255719383742</v>
       </c>
       <c r="E10" t="n">
-        <v>10.230333161966</v>
+        <v>10.21803572572909</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520220724122575</v>
+        <v>0.7520284191106232</v>
       </c>
       <c r="G10" t="n">
-        <v>28.3582551238875</v>
+        <v>28.13191652043303</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59301533096384</v>
+        <v>34.59330727908865</v>
       </c>
       <c r="I10" t="n">
-        <v>3.937375585855357</v>
+        <v>3.95538854640676</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700137952576609</v>
+        <v>4.700177619441394</v>
       </c>
       <c r="K10" t="n">
-        <v>15.59449863340672</v>
+        <v>15.83089017040672</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1634121678695</v>
+        <v>43.18123241745869</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86895791028803</v>
+        <v>99.86835992206733</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.13233544262197</v>
+        <v>81.98249632517921</v>
       </c>
       <c r="C11" t="n">
-        <v>39.44866429348387</v>
+        <v>39.28298240057669</v>
       </c>
       <c r="D11" t="n">
-        <v>1.73351606941696</v>
+        <v>1.721583629028314</v>
       </c>
       <c r="E11" t="n">
-        <v>10.21549629584518</v>
+        <v>10.2248651801157</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530248381172649</v>
+        <v>0.7530376306132993</v>
       </c>
       <c r="G11" t="n">
-        <v>26.79922896059873</v>
+        <v>26.63621316763049</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63914255339418</v>
+        <v>34.63973100821175</v>
       </c>
       <c r="I11" t="n">
-        <v>3.285521487016745</v>
+        <v>3.300580518246549</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706405238232906</v>
+        <v>4.70648519133312</v>
       </c>
       <c r="K11" t="n">
-        <v>17.86766455737803</v>
+        <v>18.01750367482078</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57429960508658</v>
+        <v>42.58964202053568</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89062845594849</v>
+        <v>99.89012809593315</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.76300132082818</v>
+        <v>79.68842960785211</v>
       </c>
       <c r="C12" t="n">
-        <v>37.58825447093668</v>
+        <v>37.50004685092827</v>
       </c>
       <c r="D12" t="n">
-        <v>1.629381298821702</v>
+        <v>1.621085955577704</v>
       </c>
       <c r="E12" t="n">
-        <v>10.05868208395821</v>
+        <v>10.08692929535291</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538874329010382</v>
+        <v>0.7539050101903344</v>
       </c>
       <c r="G12" t="n">
-        <v>25.18936124193353</v>
+        <v>25.0813206792579</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67882191344775</v>
+        <v>34.67963046875536</v>
       </c>
       <c r="I12" t="n">
-        <v>2.741070894134457</v>
+        <v>2.753651885028318</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711796455631489</v>
+        <v>4.71190631368959</v>
       </c>
       <c r="K12" t="n">
-        <v>20.2369986791718</v>
+        <v>20.31157039214789</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08348236414104</v>
+        <v>42.09669996475033</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90873551424953</v>
+        <v>99.90831720782649</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.40526996240443</v>
+        <v>77.38697994012604</v>
       </c>
       <c r="C13" t="n">
-        <v>35.65428499004273</v>
+        <v>35.62424292335115</v>
       </c>
       <c r="D13" t="n">
-        <v>1.526709759961202</v>
+        <v>1.521178389456162</v>
       </c>
       <c r="E13" t="n">
-        <v>9.80593759966033</v>
+        <v>9.848101647260695</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546297357921985</v>
+        <v>0.7546509172905782</v>
       </c>
       <c r="G13" t="n">
-        <v>23.60211430133552</v>
+        <v>23.53555828735217</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71296784644112</v>
+        <v>34.71394219536658</v>
       </c>
       <c r="I13" t="n">
-        <v>2.286474870512818</v>
+        <v>2.296980270333744</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716435848701241</v>
+        <v>4.716568233066114</v>
       </c>
       <c r="K13" t="n">
-        <v>22.59473003759557</v>
+        <v>22.61302005987396</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67484411419128</v>
+        <v>41.68624668663522</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92385914182958</v>
+        <v>99.92350966986032</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.01969010141593</v>
+        <v>83.9737737612883</v>
       </c>
       <c r="C14" t="n">
-        <v>39.6275680003739</v>
+        <v>39.67956079561313</v>
       </c>
       <c r="D14" t="n">
-        <v>1.528620809607683</v>
+        <v>1.52299437767162</v>
       </c>
       <c r="E14" t="n">
-        <v>12.05269305725323</v>
+        <v>12.12291419186383</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555743389693257</v>
+        <v>0.755551822261411</v>
       </c>
       <c r="G14" t="n">
-        <v>25.34028336151108</v>
+        <v>25.32547000576358</v>
       </c>
       <c r="H14" t="n">
-        <v>36.46504484989204</v>
+        <v>36.51719870856703</v>
       </c>
       <c r="I14" t="n">
-        <v>3.155134065624299</v>
+        <v>3.00744576602701</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722339618558285</v>
+        <v>4.722198889133819</v>
       </c>
       <c r="K14" t="n">
-        <v>15.98030989858407</v>
+        <v>16.0262262387117</v>
       </c>
       <c r="L14" t="n">
-        <v>44.28708244826704</v>
+        <v>44.19408430742549</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89496034722501</v>
+        <v>99.89987134175033</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.35548869210776</v>
+        <v>83.31843753374947</v>
       </c>
       <c r="C15" t="n">
-        <v>39.45118322270318</v>
+        <v>39.47862337331354</v>
       </c>
       <c r="D15" t="n">
-        <v>1.504116200175271</v>
+        <v>1.497634444846912</v>
       </c>
       <c r="E15" t="n">
-        <v>12.29815623980861</v>
+        <v>12.34985348413026</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563696100427504</v>
+        <v>0.7563101450591578</v>
       </c>
       <c r="G15" t="n">
-        <v>24.93406506147377</v>
+        <v>24.91444870993624</v>
       </c>
       <c r="H15" t="n">
-        <v>36.50342571311698</v>
+        <v>36.56453214185942</v>
       </c>
       <c r="I15" t="n">
-        <v>2.632045804723185</v>
+        <v>2.508720201297754</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72731006276719</v>
+        <v>4.726938406619737</v>
       </c>
       <c r="K15" t="n">
-        <v>16.64451130789225</v>
+        <v>16.68156246625053</v>
       </c>
       <c r="L15" t="n">
-        <v>43.81666285647057</v>
+        <v>43.75627400026852</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91235738706601</v>
+        <v>99.91645983983258</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.04409134966019</v>
+        <v>80.95522354747177</v>
       </c>
       <c r="C16" t="n">
-        <v>37.5468716863755</v>
+        <v>37.50346615898621</v>
       </c>
       <c r="D16" t="n">
-        <v>1.415642678339664</v>
+        <v>1.407539203257971</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94065918598288</v>
+        <v>11.95564002680906</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570525706006739</v>
+        <v>0.7569617416144933</v>
       </c>
       <c r="G16" t="n">
-        <v>23.46742003138254</v>
+        <v>23.41563617707784</v>
       </c>
       <c r="H16" t="n">
-        <v>36.53638631817056</v>
+        <v>36.59603419607188</v>
       </c>
       <c r="I16" t="n">
-        <v>2.195351998929667</v>
+        <v>2.092401317549949</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731578566254212</v>
+        <v>4.731010885090583</v>
       </c>
       <c r="K16" t="n">
-        <v>18.95590865033982</v>
+        <v>19.04477645252824</v>
       </c>
       <c r="L16" t="n">
-        <v>43.42410727982015</v>
+        <v>43.38207071622728</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92688761653547</v>
+        <v>99.93031332774173</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.63062509215416</v>
+        <v>82.70221413474783</v>
       </c>
       <c r="C17" t="n">
-        <v>38.70689760392855</v>
+        <v>38.77694629525411</v>
       </c>
       <c r="D17" t="n">
-        <v>1.416901780696981</v>
+        <v>1.408721182602717</v>
       </c>
       <c r="E17" t="n">
-        <v>12.69857536436382</v>
+        <v>12.76040818037309</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577259090714906</v>
+        <v>0.7575973993221292</v>
       </c>
       <c r="G17" t="n">
-        <v>23.86812127820961</v>
+        <v>23.88278242674073</v>
       </c>
       <c r="H17" t="n">
-        <v>36.94871137834485</v>
+        <v>37.07424866904102</v>
       </c>
       <c r="I17" t="n">
-        <v>2.204802449770601</v>
+        <v>2.083472530904842</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735786931696817</v>
+        <v>4.734983745763309</v>
       </c>
       <c r="K17" t="n">
-        <v>17.36937490784584</v>
+        <v>17.29778586525217</v>
       </c>
       <c r="L17" t="n">
-        <v>43.85029938173475</v>
+        <v>43.85587702598202</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92657189350913</v>
+        <v>99.9306091864883</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.49413592069519</v>
+        <v>80.38800899386615</v>
       </c>
       <c r="C18" t="n">
-        <v>36.91105772335108</v>
+        <v>36.78467523300485</v>
       </c>
       <c r="D18" t="n">
-        <v>1.338222542894894</v>
+        <v>1.324000107193484</v>
       </c>
       <c r="E18" t="n">
-        <v>12.29989101869658</v>
+        <v>12.28257161081584</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583028689829445</v>
+        <v>0.7581432140596321</v>
       </c>
       <c r="G18" t="n">
-        <v>22.54274670707064</v>
+        <v>22.44646199942958</v>
       </c>
       <c r="H18" t="n">
-        <v>36.97684546349355</v>
+        <v>37.10095899212755</v>
       </c>
       <c r="I18" t="n">
-        <v>1.838734388413186</v>
+        <v>1.737477982367345</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739392931143404</v>
+        <v>4.738395087872702</v>
       </c>
       <c r="K18" t="n">
-        <v>19.5058640793048</v>
+        <v>19.61199100613388</v>
       </c>
       <c r="L18" t="n">
-        <v>43.5218336848505</v>
+        <v>43.54545952389169</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93875548750638</v>
+        <v>99.94212576303042</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.70992567201988</v>
+        <v>79.48427096219876</v>
       </c>
       <c r="C19" t="n">
-        <v>36.41033266513825</v>
+        <v>36.14875528627108</v>
       </c>
       <c r="D19" t="n">
-        <v>1.310056383908381</v>
+        <v>1.291595783978557</v>
       </c>
       <c r="E19" t="n">
-        <v>12.29655331915633</v>
+        <v>12.22342404981345</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587890804149129</v>
+        <v>0.7586038423972155</v>
       </c>
       <c r="G19" t="n">
-        <v>22.06827959312522</v>
+        <v>21.89709466500926</v>
       </c>
       <c r="H19" t="n">
-        <v>37.00055441372684</v>
+        <v>37.12350058156127</v>
       </c>
       <c r="I19" t="n">
-        <v>1.533261129094997</v>
+        <v>1.448778024456424</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742431752593206</v>
+        <v>4.741274014982597</v>
       </c>
       <c r="K19" t="n">
-        <v>20.2900743279801</v>
+        <v>20.51572903780124</v>
       </c>
       <c r="L19" t="n">
-        <v>43.24851705164794</v>
+        <v>43.28725239863971</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9489240447663</v>
+        <v>99.95173672271203</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.37466204288209</v>
+        <v>76.92315627369899</v>
       </c>
       <c r="C20" t="n">
-        <v>34.31136768206356</v>
+        <v>33.8108228227621</v>
       </c>
       <c r="D20" t="n">
-        <v>1.224974912806236</v>
+        <v>1.19881072507698</v>
       </c>
       <c r="E20" t="n">
-        <v>11.71102520325333</v>
+        <v>11.54664787887216</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592069829962662</v>
+        <v>0.7590009283835035</v>
       </c>
       <c r="G20" t="n">
-        <v>20.63505754593748</v>
+        <v>20.32406133409525</v>
       </c>
       <c r="H20" t="n">
-        <v>37.02093244446042</v>
+        <v>37.14293262371427</v>
       </c>
       <c r="I20" t="n">
-        <v>1.278421309701704</v>
+        <v>1.207946981159926</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745043643726665</v>
+        <v>4.743755802396898</v>
       </c>
       <c r="K20" t="n">
-        <v>22.62533795711791</v>
+        <v>23.07684372630101</v>
       </c>
       <c r="L20" t="n">
-        <v>43.02070377389921</v>
+        <v>43.07208961692422</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95740941308067</v>
+        <v>99.95975616598733</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.80371702988991</v>
+        <v>82.62266311827273</v>
       </c>
       <c r="C21" t="n">
-        <v>37.56267976768773</v>
+        <v>37.30241421369931</v>
       </c>
       <c r="D21" t="n">
-        <v>1.225940563178415</v>
+        <v>1.199675100863092</v>
       </c>
       <c r="E21" t="n">
-        <v>13.50092452389637</v>
+        <v>13.44210547251184</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598054675023789</v>
+        <v>0.7595481891064916</v>
       </c>
       <c r="G21" t="n">
-        <v>22.1056199547825</v>
+        <v>21.92798152658273</v>
       </c>
       <c r="H21" t="n">
-        <v>38.50441187391444</v>
+        <v>38.75897968893352</v>
       </c>
       <c r="I21" t="n">
-        <v>1.958230474725935</v>
+        <v>1.787196958359474</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748784171889869</v>
+        <v>4.747176181915573</v>
       </c>
       <c r="K21" t="n">
-        <v>17.19628297011009</v>
+        <v>17.37733688172728</v>
       </c>
       <c r="L21" t="n">
-        <v>45.17581432842437</v>
+        <v>45.26071859563213</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9347770662222</v>
+        <v>99.94046969105872</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_95_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.75936562476237</v>
+        <v>45.02653639929796</v>
       </c>
       <c r="M2" t="n">
-        <v>101.5641723294113</v>
+        <v>100.5803874306216</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02864858545945</v>
+        <v>88.1138937386192</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91298220052779</v>
+        <v>45.95533840986597</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228745960498927</v>
+        <v>2.228932329882918</v>
       </c>
       <c r="E3" t="n">
-        <v>5.697513733557122</v>
+        <v>5.726356420487303</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429153201663089</v>
+        <v>0.7429774432943059</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96764732489657</v>
+        <v>33.98145860319401</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1741047276502</v>
+        <v>34.17696239153807</v>
       </c>
       <c r="I3" t="n">
-        <v>6.574500767650891</v>
+        <v>6.613597529633184</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64322075103943</v>
+        <v>4.643609020589412</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97135141454056</v>
+        <v>11.88610626138081</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87967714670805</v>
+        <v>48.9211825762128</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640107617764</v>
+        <v>106.7626272474596</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.15404464239171</v>
+        <v>87.31631290489334</v>
       </c>
       <c r="C4" t="n">
-        <v>42.67534350266938</v>
+        <v>42.80069917558171</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186799518095307</v>
+        <v>2.191151138490414</v>
       </c>
       <c r="E4" t="n">
-        <v>6.50532534742488</v>
+        <v>6.549784554943328</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444753145504198</v>
+        <v>0.7445439426038245</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32835420340449</v>
+        <v>33.40546086020683</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2458644693193</v>
+        <v>34.24902135977592</v>
       </c>
       <c r="I4" t="n">
-        <v>5.490255073657183</v>
+        <v>5.522951407599105</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652970715940123</v>
+        <v>4.653399641273904</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84595535760828</v>
+        <v>12.68368709510668</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29607611839871</v>
+        <v>44.33190268682181</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81737497867638</v>
+        <v>99.81628895751021</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.0044915007514</v>
+        <v>86.31603863642459</v>
       </c>
       <c r="C5" t="n">
-        <v>42.37793666873163</v>
+        <v>42.65774281216443</v>
       </c>
       <c r="D5" t="n">
-        <v>2.130753650662294</v>
+        <v>2.142956650423109</v>
       </c>
       <c r="E5" t="n">
-        <v>7.102489217435981</v>
+        <v>7.174164077484285</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457977972062622</v>
+        <v>0.7458696269955398</v>
       </c>
       <c r="G5" t="n">
-        <v>32.47417598268151</v>
+        <v>32.67070593776948</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30669867148805</v>
+        <v>34.31000284179483</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583339948738177</v>
+        <v>4.610654333235226</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661236232539138</v>
+        <v>4.661685168722125</v>
       </c>
       <c r="K5" t="n">
-        <v>13.99550849924859</v>
+        <v>13.68396136357542</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47404774664041</v>
+        <v>43.50488050738241</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84749291462063</v>
+        <v>99.84658468312226</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.6903585239572</v>
+        <v>85.02648558142214</v>
       </c>
       <c r="C6" t="n">
-        <v>41.77565866407213</v>
+        <v>42.08451189506376</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066723972177551</v>
+        <v>2.080274472601747</v>
       </c>
       <c r="E6" t="n">
-        <v>7.526591042221253</v>
+        <v>7.605652136122845</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469206428552702</v>
+        <v>0.7469948106620473</v>
       </c>
       <c r="G6" t="n">
-        <v>31.49831889728744</v>
+        <v>31.71507718123987</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35834957134242</v>
+        <v>34.36176129045417</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825200380227823</v>
+        <v>3.84800812370367</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668254017845438</v>
+        <v>4.668717566637796</v>
       </c>
       <c r="K6" t="n">
-        <v>15.30964147604281</v>
+        <v>14.97351441857786</v>
       </c>
       <c r="L6" t="n">
-        <v>42.787384861309</v>
+        <v>42.81389995487964</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87268500142393</v>
+        <v>99.87192626852125</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.21760686055879</v>
+        <v>83.6026781141865</v>
       </c>
       <c r="C7" t="n">
-        <v>40.89708072173032</v>
+        <v>41.2586367061275</v>
       </c>
       <c r="D7" t="n">
-        <v>1.995198751188205</v>
+        <v>2.011304006013781</v>
       </c>
       <c r="E7" t="n">
-        <v>7.798067696530416</v>
+        <v>7.888620274208417</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478755602584323</v>
+        <v>0.7479510937853011</v>
       </c>
       <c r="G7" t="n">
-        <v>30.40822450139788</v>
+        <v>30.6635795544254</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40227577188787</v>
+        <v>34.40575031412384</v>
       </c>
       <c r="I7" t="n">
-        <v>3.191742327680787</v>
+        <v>3.21077853547164</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674222251615202</v>
+        <v>4.674694336158132</v>
       </c>
       <c r="K7" t="n">
-        <v>16.78239313944121</v>
+        <v>16.39732188581349</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21427057271104</v>
+        <v>42.23715229351169</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89374443388257</v>
+        <v>99.89311088545267</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.20705625071328</v>
+        <v>88.43878006576983</v>
       </c>
       <c r="C8" t="n">
-        <v>43.27744168956789</v>
+        <v>43.59246106219699</v>
       </c>
       <c r="D8" t="n">
-        <v>1.999478703515501</v>
+        <v>2.015542902234424</v>
       </c>
       <c r="E8" t="n">
-        <v>9.685533716579647</v>
+        <v>9.739768019356211</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494798474216785</v>
+        <v>0.7495274278726358</v>
       </c>
       <c r="G8" t="n">
-        <v>30.93578497899414</v>
+        <v>31.17949540721082</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47607298139719</v>
+        <v>34.47826168214124</v>
       </c>
       <c r="I8" t="n">
-        <v>5.676456976419634</v>
+        <v>5.591638202750528</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68424904638549</v>
+        <v>4.684546424203974</v>
       </c>
       <c r="K8" t="n">
-        <v>11.79294374928671</v>
+        <v>11.56121993423017</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74080435025371</v>
+        <v>44.66032305669248</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81118978910831</v>
+        <v>99.81400405311965</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.26759849157881</v>
+        <v>86.5225065087307</v>
       </c>
       <c r="C9" t="n">
-        <v>42.21921628965699</v>
+        <v>42.54467661668365</v>
       </c>
       <c r="D9" t="n">
-        <v>1.911987219332034</v>
+        <v>1.929047833479523</v>
       </c>
       <c r="E9" t="n">
-        <v>10.05156285851228</v>
+        <v>10.09980841037909</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750852250324952</v>
+        <v>0.7508753826947713</v>
       </c>
       <c r="G9" t="n">
-        <v>29.58212327835486</v>
+        <v>29.84145760310351</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53920351494777</v>
+        <v>34.54026760395947</v>
       </c>
       <c r="I9" t="n">
-        <v>4.739042805575967</v>
+        <v>4.668078533272013</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692826564530949</v>
+        <v>4.692971141842321</v>
       </c>
       <c r="K9" t="n">
-        <v>13.73240150842119</v>
+        <v>13.47749349126929</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89070284146571</v>
+        <v>43.82250660863732</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84232063954389</v>
+        <v>99.84467671659027</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.1691098295933</v>
+        <v>84.29707506858108</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85623733420192</v>
+        <v>41.04410203023949</v>
       </c>
       <c r="D10" t="n">
-        <v>1.818255719383742</v>
+        <v>1.829331768585162</v>
       </c>
       <c r="E10" t="n">
-        <v>10.21803572572909</v>
+        <v>10.22707364161499</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520284191106232</v>
+        <v>0.752032186145748</v>
       </c>
       <c r="G10" t="n">
-        <v>28.13191652043303</v>
+        <v>28.29889724184692</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59330727908865</v>
+        <v>34.5934805627044</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95538854640676</v>
+        <v>3.896058504272933</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700177619441394</v>
+        <v>4.700201163410926</v>
       </c>
       <c r="K10" t="n">
-        <v>15.83089017040672</v>
+        <v>15.70292493141891</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18123241745869</v>
+        <v>43.12330419019514</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86835992206733</v>
+        <v>99.87033115185355</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.98249632517921</v>
+        <v>81.92248626281418</v>
       </c>
       <c r="C11" t="n">
-        <v>39.28298240057669</v>
+        <v>39.27386526913046</v>
       </c>
       <c r="D11" t="n">
-        <v>1.721583629028314</v>
+        <v>1.723967584515905</v>
       </c>
       <c r="E11" t="n">
-        <v>10.2248651801157</v>
+        <v>10.17985900315656</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530376306132993</v>
+        <v>0.7530269737794199</v>
       </c>
       <c r="G11" t="n">
-        <v>26.63621316763049</v>
+        <v>26.66896314834292</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63973100821175</v>
+        <v>34.63924079385331</v>
       </c>
       <c r="I11" t="n">
-        <v>3.300580518246549</v>
+        <v>3.251010173044671</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70648519133312</v>
+        <v>4.706418586121375</v>
       </c>
       <c r="K11" t="n">
-        <v>18.01750367482078</v>
+        <v>18.07751373718585</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58964202053568</v>
+        <v>42.54039714634277</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89012809593315</v>
+        <v>99.89177615265908</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.68842960785211</v>
+        <v>79.46485732286077</v>
       </c>
       <c r="C12" t="n">
-        <v>37.50004685092827</v>
+        <v>37.31971696054203</v>
       </c>
       <c r="D12" t="n">
-        <v>1.621085955577704</v>
+        <v>1.615963035393443</v>
       </c>
       <c r="E12" t="n">
-        <v>10.08692929535291</v>
+        <v>9.994145668277371</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539050101903344</v>
+        <v>0.7538837059528593</v>
       </c>
       <c r="G12" t="n">
-        <v>25.0813206792579</v>
+        <v>24.998183856278</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67963046875536</v>
+        <v>34.67865047383152</v>
       </c>
       <c r="I12" t="n">
-        <v>2.753651885028318</v>
+        <v>2.712257420922178</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71190631368959</v>
+        <v>4.711773162205371</v>
       </c>
       <c r="K12" t="n">
-        <v>20.31157039214789</v>
+        <v>20.53514267713928</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09669996475033</v>
+        <v>42.05483452417857</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90831720782649</v>
+        <v>99.90969416185987</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.38697994012604</v>
+        <v>77.00577980761018</v>
       </c>
       <c r="C13" t="n">
-        <v>35.62424292335115</v>
+        <v>35.27980117022362</v>
       </c>
       <c r="D13" t="n">
-        <v>1.521178389456162</v>
+        <v>1.50889071019223</v>
       </c>
       <c r="E13" t="n">
-        <v>9.848101647260695</v>
+        <v>9.709013481777413</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546509172905782</v>
+        <v>0.7546220088108835</v>
       </c>
       <c r="G13" t="n">
-        <v>23.53555828735217</v>
+        <v>23.34182562736132</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71394219536658</v>
+        <v>34.71261240530064</v>
       </c>
       <c r="I13" t="n">
-        <v>2.296980270333744</v>
+        <v>2.262428019099654</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716568233066114</v>
+        <v>4.716387555068022</v>
       </c>
       <c r="K13" t="n">
-        <v>22.61302005987396</v>
+        <v>22.99422019238985</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68624668663522</v>
+        <v>41.65063815347204</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92350966986032</v>
+        <v>99.9246595160855</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.9737737612883</v>
+        <v>83.80655267482398</v>
       </c>
       <c r="C14" t="n">
-        <v>39.67956079561313</v>
+        <v>39.56334031753221</v>
       </c>
       <c r="D14" t="n">
-        <v>1.52299437767162</v>
+        <v>1.510591814970491</v>
       </c>
       <c r="E14" t="n">
-        <v>12.12291419186383</v>
+        <v>12.08305486199759</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755551822261411</v>
+        <v>0.7554727603572331</v>
       </c>
       <c r="G14" t="n">
-        <v>25.32547000576358</v>
+        <v>25.25882410216557</v>
       </c>
       <c r="H14" t="n">
-        <v>36.51719870856703</v>
+        <v>36.64243016488799</v>
       </c>
       <c r="I14" t="n">
-        <v>3.00744576602701</v>
+        <v>2.834474218212375</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722198889133819</v>
+        <v>4.721704752232707</v>
       </c>
       <c r="K14" t="n">
-        <v>16.0262262387117</v>
+        <v>16.19344732517606</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19408430742549</v>
+        <v>44.14883628177498</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89987134175033</v>
+        <v>99.90562392448324</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.31843753374947</v>
+        <v>82.96822849269054</v>
       </c>
       <c r="C15" t="n">
-        <v>39.47862337331354</v>
+        <v>39.14949950437219</v>
       </c>
       <c r="D15" t="n">
-        <v>1.497634444846912</v>
+        <v>1.477790730786131</v>
       </c>
       <c r="E15" t="n">
-        <v>12.34985348413026</v>
+        <v>12.22854351600871</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563101450591578</v>
+        <v>0.756190371768981</v>
       </c>
       <c r="G15" t="n">
-        <v>24.91444870993624</v>
+        <v>24.72416236507006</v>
       </c>
       <c r="H15" t="n">
-        <v>36.56453214185942</v>
+        <v>36.69104615247015</v>
       </c>
       <c r="I15" t="n">
-        <v>2.508720201297754</v>
+        <v>2.364305533030379</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726938406619737</v>
+        <v>4.726189823556131</v>
       </c>
       <c r="K15" t="n">
-        <v>16.68156246625053</v>
+        <v>17.03177150730945</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75627400026852</v>
+        <v>43.73999359336803</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91645983983258</v>
+        <v>99.92126460504969</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.95522354747177</v>
+        <v>80.46871847263223</v>
       </c>
       <c r="C16" t="n">
-        <v>37.50346615898621</v>
+        <v>37.01555273205203</v>
       </c>
       <c r="D16" t="n">
-        <v>1.407539203257971</v>
+        <v>1.382804172272062</v>
       </c>
       <c r="E16" t="n">
-        <v>11.95564002680906</v>
+        <v>11.77118497231347</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569617416144933</v>
+        <v>0.7568080463847516</v>
       </c>
       <c r="G16" t="n">
-        <v>23.41563617707784</v>
+        <v>23.13499074132347</v>
       </c>
       <c r="H16" t="n">
-        <v>36.59603419607188</v>
+        <v>36.72101628787591</v>
       </c>
       <c r="I16" t="n">
-        <v>2.092401317549949</v>
+        <v>1.971863962557859</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731010885090583</v>
+        <v>4.730050289904698</v>
       </c>
       <c r="K16" t="n">
-        <v>19.04477645252824</v>
+        <v>19.53128152736775</v>
       </c>
       <c r="L16" t="n">
-        <v>43.38207071622728</v>
+        <v>43.38749058688493</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93031332774173</v>
+        <v>99.93432484630472</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.70221413474783</v>
+        <v>82.18799432221745</v>
       </c>
       <c r="C17" t="n">
-        <v>38.77694629525411</v>
+        <v>38.26887433032927</v>
       </c>
       <c r="D17" t="n">
-        <v>1.408721182602717</v>
+        <v>1.383901027052966</v>
       </c>
       <c r="E17" t="n">
-        <v>12.76040818037309</v>
+        <v>12.5555312302529</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575973993221292</v>
+        <v>0.7574083544692576</v>
       </c>
       <c r="G17" t="n">
-        <v>23.88278242674073</v>
+        <v>23.60238899127513</v>
       </c>
       <c r="H17" t="n">
-        <v>37.07424866904102</v>
+        <v>37.19919111586589</v>
       </c>
       <c r="I17" t="n">
-        <v>2.083472530904842</v>
+        <v>1.955771387868441</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734983745763309</v>
+        <v>4.73380221543286</v>
       </c>
       <c r="K17" t="n">
-        <v>17.29778586525217</v>
+        <v>17.81200567778256</v>
       </c>
       <c r="L17" t="n">
-        <v>43.85587702598202</v>
+        <v>43.85397928258674</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9306091864883</v>
+        <v>99.93485929069857</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.38800899386615</v>
+        <v>79.76144779153877</v>
       </c>
       <c r="C18" t="n">
-        <v>36.78467523300485</v>
+        <v>36.1443179873533</v>
       </c>
       <c r="D18" t="n">
-        <v>1.324000107193484</v>
+        <v>1.295333720101004</v>
       </c>
       <c r="E18" t="n">
-        <v>12.28257161081584</v>
+        <v>12.02381868829596</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581432140596321</v>
+        <v>0.7579245907901426</v>
       </c>
       <c r="G18" t="n">
-        <v>22.44646199942958</v>
+        <v>22.09187632474334</v>
       </c>
       <c r="H18" t="n">
-        <v>37.10095899212755</v>
+        <v>37.22454543556442</v>
       </c>
       <c r="I18" t="n">
-        <v>1.737477982367345</v>
+        <v>1.630920339605504</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738395087872702</v>
+        <v>4.737028692438392</v>
       </c>
       <c r="K18" t="n">
-        <v>19.61199100613388</v>
+        <v>20.23855220846123</v>
       </c>
       <c r="L18" t="n">
-        <v>43.54545952389169</v>
+        <v>43.56280282118912</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94212576303042</v>
+        <v>99.94567301700366</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.48427096219876</v>
+        <v>78.76339325792441</v>
       </c>
       <c r="C19" t="n">
-        <v>36.14875528627108</v>
+        <v>35.3974155041502</v>
       </c>
       <c r="D19" t="n">
-        <v>1.291595783978557</v>
+        <v>1.259549404536882</v>
       </c>
       <c r="E19" t="n">
-        <v>12.22342404981345</v>
+        <v>11.91830107665939</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586038423972155</v>
+        <v>0.7583607868102057</v>
       </c>
       <c r="G19" t="n">
-        <v>21.89709466500926</v>
+        <v>21.48157593532204</v>
       </c>
       <c r="H19" t="n">
-        <v>37.12350058156127</v>
+        <v>37.24596867313311</v>
       </c>
       <c r="I19" t="n">
-        <v>1.448778024456424</v>
+        <v>1.359882463898988</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741274014982597</v>
+        <v>4.739754917563785</v>
       </c>
       <c r="K19" t="n">
-        <v>20.51572903780124</v>
+        <v>21.23660674207558</v>
       </c>
       <c r="L19" t="n">
-        <v>43.28725239863971</v>
+        <v>43.3206744110074</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95173672271203</v>
+        <v>99.95469665723319</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.92315627369899</v>
+        <v>76.17857917984412</v>
       </c>
       <c r="C20" t="n">
-        <v>33.8108228227621</v>
+        <v>33.02184568967863</v>
       </c>
       <c r="D20" t="n">
-        <v>1.19881072507698</v>
+        <v>1.166193611207169</v>
       </c>
       <c r="E20" t="n">
-        <v>11.54664787887216</v>
+        <v>11.22390187305867</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590009283835035</v>
+        <v>0.7587370201510402</v>
       </c>
       <c r="G20" t="n">
-        <v>20.32406133409525</v>
+        <v>19.88939578249045</v>
       </c>
       <c r="H20" t="n">
-        <v>37.14293262371427</v>
+        <v>37.2644469165632</v>
       </c>
       <c r="I20" t="n">
-        <v>1.207946981159926</v>
+        <v>1.133797600429595</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743755802396898</v>
+        <v>4.742106375944001</v>
       </c>
       <c r="K20" t="n">
-        <v>23.07684372630101</v>
+        <v>23.82142082015588</v>
       </c>
       <c r="L20" t="n">
-        <v>43.07208961692422</v>
+        <v>43.11895897727939</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95975616598733</v>
+        <v>99.9622254871139</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.62266311827273</v>
+        <v>82.17866771902708</v>
       </c>
       <c r="C21" t="n">
-        <v>37.30241421369931</v>
+        <v>36.80144596342874</v>
       </c>
       <c r="D21" t="n">
-        <v>1.199675100863092</v>
+        <v>1.166935527646295</v>
       </c>
       <c r="E21" t="n">
-        <v>13.44210547251184</v>
+        <v>13.24455062167154</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595481891064916</v>
+        <v>0.7592197182749313</v>
       </c>
       <c r="G21" t="n">
-        <v>21.92798152658273</v>
+        <v>21.65415267285706</v>
       </c>
       <c r="H21" t="n">
-        <v>38.75897968893352</v>
+        <v>39.04025757702694</v>
       </c>
       <c r="I21" t="n">
-        <v>1.787196958359474</v>
+        <v>1.568428362331996</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747176181915573</v>
+        <v>4.745123239218321</v>
       </c>
       <c r="K21" t="n">
-        <v>17.37733688172728</v>
+        <v>17.82133228097291</v>
       </c>
       <c r="L21" t="n">
-        <v>45.26071859563213</v>
+        <v>45.32497404946396</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94046969105872</v>
+        <v>99.94775229386562</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_95_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.02653639929796</v>
+        <v>44.19710151805096</v>
       </c>
       <c r="M2" t="n">
-        <v>100.5803874306216</v>
+        <v>94.90337679302272</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.1138937386192</v>
+        <v>81.37592757739813</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95533840986597</v>
+        <v>43.1314831329537</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228932329882918</v>
+        <v>2.173649823885189</v>
       </c>
       <c r="E3" t="n">
-        <v>5.726356420487303</v>
+        <v>4.158631294355039</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429774432943059</v>
+        <v>0.7375616317831909</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98145860319401</v>
+        <v>32.69531610093971</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17696239153807</v>
+        <v>33.92783506202677</v>
       </c>
       <c r="I3" t="n">
-        <v>6.613597529633184</v>
+        <v>3.073173465763295</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643609020589412</v>
+        <v>4.609760198644943</v>
       </c>
       <c r="K3" t="n">
-        <v>11.88610626138081</v>
+        <v>18.62407242260185</v>
       </c>
       <c r="L3" t="n">
-        <v>48.9211825762128</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7626272474596</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.31631290489334</v>
+        <v>88.41768022272333</v>
       </c>
       <c r="C4" t="n">
-        <v>42.80069917558171</v>
+        <v>42.738244060623</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191151138490414</v>
+        <v>2.179328302833836</v>
       </c>
       <c r="E4" t="n">
-        <v>6.549784554943328</v>
+        <v>6.541703166908056</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445439426038245</v>
+        <v>0.7394884500560277</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40546086020683</v>
+        <v>33.38937424036438</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24902135977592</v>
+        <v>34.01646870257727</v>
       </c>
       <c r="I4" t="n">
-        <v>5.522951407599105</v>
+        <v>6.929514547133576</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653399641273904</v>
+        <v>4.621802812850173</v>
       </c>
       <c r="K4" t="n">
-        <v>12.68368709510668</v>
+        <v>11.58231977727669</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33190268682181</v>
+        <v>45.4490541975381</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81628895751021</v>
+        <v>99.76961803543777</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.31603863642459</v>
+        <v>87.20690086101118</v>
       </c>
       <c r="C5" t="n">
-        <v>42.65774281216443</v>
+        <v>42.60154737444094</v>
       </c>
       <c r="D5" t="n">
-        <v>2.142956650423109</v>
+        <v>2.121349496243276</v>
       </c>
       <c r="E5" t="n">
-        <v>7.174164077484285</v>
+        <v>7.332229421094597</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458696269955398</v>
+        <v>0.7411242888518261</v>
       </c>
       <c r="G5" t="n">
-        <v>32.67070593776948</v>
+        <v>32.50108399573046</v>
       </c>
       <c r="H5" t="n">
-        <v>34.31000284179483</v>
+        <v>34.091717287184</v>
       </c>
       <c r="I5" t="n">
-        <v>4.610654333235226</v>
+        <v>5.787369566583103</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661685168722125</v>
+        <v>4.632026805323913</v>
       </c>
       <c r="K5" t="n">
-        <v>13.68396136357542</v>
+        <v>12.79309913898883</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50488050738241</v>
+        <v>44.41286697137209</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84658468312226</v>
+        <v>99.80751348480186</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.02648558142214</v>
+        <v>85.71303214300461</v>
       </c>
       <c r="C6" t="n">
-        <v>42.08451189506376</v>
+        <v>42.0057198126057</v>
       </c>
       <c r="D6" t="n">
-        <v>2.080274472601747</v>
+        <v>2.049659426272216</v>
       </c>
       <c r="E6" t="n">
-        <v>7.605652136122845</v>
+        <v>7.889751706172366</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469948106620473</v>
+        <v>0.7425169267678821</v>
       </c>
       <c r="G6" t="n">
-        <v>31.71507718123987</v>
+        <v>31.40272420640039</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36176129045417</v>
+        <v>34.15577863132257</v>
       </c>
       <c r="I6" t="n">
-        <v>3.84800812370367</v>
+        <v>4.831870453769916</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668717566637796</v>
+        <v>4.640730792299263</v>
       </c>
       <c r="K6" t="n">
-        <v>14.97351441857786</v>
+        <v>14.28696785699538</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81389995487964</v>
+        <v>43.5465520646605</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87192626852125</v>
+        <v>99.8392397342616</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.6026781141865</v>
+        <v>84.11067363095283</v>
       </c>
       <c r="C7" t="n">
-        <v>41.2586367061275</v>
+        <v>41.15338687214024</v>
       </c>
       <c r="D7" t="n">
-        <v>2.011304006013781</v>
+        <v>1.973366710000325</v>
       </c>
       <c r="E7" t="n">
-        <v>7.888620274208417</v>
+        <v>8.268243959072139</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479510937853011</v>
+        <v>0.7437036832222704</v>
       </c>
       <c r="G7" t="n">
-        <v>30.6635795544254</v>
+        <v>30.23384751530998</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40575031412384</v>
+        <v>34.21036942822443</v>
       </c>
       <c r="I7" t="n">
-        <v>3.21077853547164</v>
+        <v>4.032994314984492</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674694336158132</v>
+        <v>4.648148020139191</v>
       </c>
       <c r="K7" t="n">
-        <v>16.39732188581349</v>
+        <v>15.88932636904716</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23715229351169</v>
+        <v>42.82306813509676</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89311088545267</v>
+        <v>99.86578137628416</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.43878006576983</v>
+        <v>82.24847109794085</v>
       </c>
       <c r="C8" t="n">
-        <v>43.59246106219699</v>
+        <v>39.91709743389611</v>
       </c>
       <c r="D8" t="n">
-        <v>2.015542902234424</v>
+        <v>1.885143365793642</v>
       </c>
       <c r="E8" t="n">
-        <v>9.739768019356211</v>
+        <v>8.45949749765092</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495274278726358</v>
+        <v>0.7447180362912008</v>
       </c>
       <c r="G8" t="n">
-        <v>31.17949540721082</v>
+        <v>28.882182301481</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47826168214124</v>
+        <v>34.25702966939523</v>
       </c>
       <c r="I8" t="n">
-        <v>5.591638202750528</v>
+        <v>3.365412500508833</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684546424203974</v>
+        <v>4.654487726820006</v>
       </c>
       <c r="K8" t="n">
-        <v>11.56121993423017</v>
+        <v>17.75152890205916</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66032305669248</v>
+        <v>42.21934604418403</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81400405311965</v>
+        <v>99.8879723801393</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.5225065087307</v>
+        <v>80.33863270983008</v>
       </c>
       <c r="C9" t="n">
-        <v>42.54467661668365</v>
+        <v>38.52912121595449</v>
       </c>
       <c r="D9" t="n">
-        <v>1.929047833479523</v>
+        <v>1.795450515328719</v>
       </c>
       <c r="E9" t="n">
-        <v>10.09980841037909</v>
+        <v>8.524967731299565</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508753826947713</v>
+        <v>0.7455856150029524</v>
       </c>
       <c r="G9" t="n">
-        <v>29.84145760310351</v>
+        <v>27.50800285960244</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54026760395947</v>
+        <v>34.2969382901358</v>
       </c>
       <c r="I9" t="n">
-        <v>4.668078533272013</v>
+        <v>2.807777604692153</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692971141842321</v>
+        <v>4.659910093768453</v>
       </c>
       <c r="K9" t="n">
-        <v>13.47749349126929</v>
+        <v>19.66136729016989</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82250660863732</v>
+        <v>41.71602781330594</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84467671659027</v>
+        <v>99.90651631943032</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.29707506858108</v>
+        <v>85.45428856920068</v>
       </c>
       <c r="C10" t="n">
-        <v>41.04410203023949</v>
+        <v>42.09395854159602</v>
       </c>
       <c r="D10" t="n">
-        <v>1.829331768585162</v>
+        <v>1.797401467514238</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22707364161499</v>
+        <v>10.52825778863237</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752032186145748</v>
+        <v>0.746395774833403</v>
       </c>
       <c r="G10" t="n">
-        <v>28.29889724184692</v>
+        <v>29.06764317300867</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5934805627044</v>
+        <v>35.86395551997747</v>
       </c>
       <c r="I10" t="n">
-        <v>3.896058504272933</v>
+        <v>2.785661252525753</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700201163410926</v>
+        <v>4.664973592708769</v>
       </c>
       <c r="K10" t="n">
-        <v>15.70292493141891</v>
+        <v>14.54571143079934</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12330419019514</v>
+        <v>43.26757544046358</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87033115185355</v>
+        <v>99.90724541285894</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.92248626281418</v>
+        <v>85.14292728479879</v>
       </c>
       <c r="C11" t="n">
-        <v>39.27386526913046</v>
+        <v>42.09324780019514</v>
       </c>
       <c r="D11" t="n">
-        <v>1.723967584515905</v>
+        <v>1.775871975261113</v>
       </c>
       <c r="E11" t="n">
-        <v>10.17985900315656</v>
+        <v>10.84616117235053</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530269737794199</v>
+        <v>0.747096784196208</v>
       </c>
       <c r="G11" t="n">
-        <v>26.66896314834292</v>
+        <v>28.76365153378806</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63924079385331</v>
+        <v>35.94182278810229</v>
       </c>
       <c r="I11" t="n">
-        <v>3.251010173044671</v>
+        <v>2.398968129874289</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706418586121375</v>
+        <v>4.6693549012263</v>
       </c>
       <c r="K11" t="n">
-        <v>18.07751373718585</v>
+        <v>14.85707271520121</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54039714634277</v>
+        <v>42.96978891290552</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89177615265908</v>
+        <v>99.92010942830188</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.46485732286077</v>
+        <v>83.17355120755674</v>
       </c>
       <c r="C12" t="n">
-        <v>37.31971696054203</v>
+        <v>40.49659540639194</v>
       </c>
       <c r="D12" t="n">
-        <v>1.615963035393443</v>
+        <v>1.692721660524263</v>
       </c>
       <c r="E12" t="n">
-        <v>9.994145668277371</v>
+        <v>10.67177672561993</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538837059528593</v>
+        <v>0.7476958322931856</v>
       </c>
       <c r="G12" t="n">
-        <v>24.998183856278</v>
+        <v>27.41687276181948</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67865047383152</v>
+        <v>35.97064218740714</v>
       </c>
       <c r="I12" t="n">
-        <v>2.712257420922178</v>
+        <v>2.000743088060316</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711773162205371</v>
+        <v>4.67309895183241</v>
       </c>
       <c r="K12" t="n">
-        <v>20.53514267713928</v>
+        <v>16.82644879244327</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05483452417857</v>
+        <v>42.61031779755717</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90969416185987</v>
+        <v>99.93336199639238</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.00577980761018</v>
+        <v>84.40650851436622</v>
       </c>
       <c r="C13" t="n">
-        <v>35.27980117022362</v>
+        <v>41.52480870374734</v>
       </c>
       <c r="D13" t="n">
-        <v>1.50889071019223</v>
+        <v>1.693946982385909</v>
       </c>
       <c r="E13" t="n">
-        <v>9.709013481777413</v>
+        <v>11.33048280918257</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546220088108835</v>
+        <v>0.7482370719255108</v>
       </c>
       <c r="G13" t="n">
-        <v>23.34182562736132</v>
+        <v>27.78220068400304</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71261240530064</v>
+        <v>36.34216198444</v>
       </c>
       <c r="I13" t="n">
-        <v>2.262428019099654</v>
+        <v>1.832997282894749</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716387555068022</v>
+        <v>4.676481699534443</v>
       </c>
       <c r="K13" t="n">
-        <v>22.99422019238985</v>
+        <v>15.59349148563379</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65063815347204</v>
+        <v>42.82064409800013</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9246595160855</v>
+        <v>99.93894428738126</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.80655267482398</v>
+        <v>82.43632740400668</v>
       </c>
       <c r="C14" t="n">
-        <v>39.56334031753221</v>
+        <v>39.83926939309508</v>
       </c>
       <c r="D14" t="n">
-        <v>1.510591814970491</v>
+        <v>1.613158049551943</v>
       </c>
       <c r="E14" t="n">
-        <v>12.08305486199759</v>
+        <v>11.04484160284743</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554727603572331</v>
+        <v>0.7486995042995163</v>
       </c>
       <c r="G14" t="n">
-        <v>25.25882410216557</v>
+        <v>26.45719206898821</v>
       </c>
       <c r="H14" t="n">
-        <v>36.64243016488799</v>
+        <v>36.36462250246767</v>
       </c>
       <c r="I14" t="n">
-        <v>2.834474218212375</v>
+        <v>1.528441773979938</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721704752232707</v>
+        <v>4.679371901871977</v>
       </c>
       <c r="K14" t="n">
-        <v>16.19344732517606</v>
+        <v>17.56367259599333</v>
       </c>
       <c r="L14" t="n">
-        <v>44.14883628177498</v>
+        <v>42.54614141972007</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90562392448324</v>
+        <v>99.94908340880846</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.96822849269054</v>
+        <v>81.58918712748915</v>
       </c>
       <c r="C15" t="n">
-        <v>39.14949950437219</v>
+        <v>39.19778877195517</v>
       </c>
       <c r="D15" t="n">
-        <v>1.477790730786131</v>
+        <v>1.57756491019872</v>
       </c>
       <c r="E15" t="n">
-        <v>12.22854351600871</v>
+        <v>11.01858439435823</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756190371768981</v>
+        <v>0.7490985682371065</v>
       </c>
       <c r="G15" t="n">
-        <v>24.72416236507006</v>
+        <v>25.8734336923877</v>
       </c>
       <c r="H15" t="n">
-        <v>36.69104615247015</v>
+        <v>36.38400519119858</v>
       </c>
       <c r="I15" t="n">
-        <v>2.364305533030379</v>
+        <v>1.304634319626905</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726189823556131</v>
+        <v>4.681866051481916</v>
       </c>
       <c r="K15" t="n">
-        <v>17.03177150730945</v>
+        <v>18.41081287251086</v>
       </c>
       <c r="L15" t="n">
-        <v>43.73999359336803</v>
+        <v>42.34793371194706</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92126460504969</v>
+        <v>99.9565353564131</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.46871847263223</v>
+        <v>79.25369769637935</v>
       </c>
       <c r="C16" t="n">
-        <v>37.01555273205203</v>
+        <v>37.06439134513127</v>
       </c>
       <c r="D16" t="n">
-        <v>1.382804172272062</v>
+        <v>1.482468780769107</v>
       </c>
       <c r="E16" t="n">
-        <v>11.77118497231347</v>
+        <v>10.53566262334001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568080463847516</v>
+        <v>0.749441260550763</v>
       </c>
       <c r="G16" t="n">
-        <v>23.13499074132347</v>
+        <v>24.3137746360197</v>
       </c>
       <c r="H16" t="n">
-        <v>36.72101628787591</v>
+        <v>36.40064988850244</v>
       </c>
       <c r="I16" t="n">
-        <v>1.971863962557859</v>
+        <v>1.087692628755071</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730050289904698</v>
+        <v>4.684007878442269</v>
       </c>
       <c r="K16" t="n">
-        <v>19.53128152736775</v>
+        <v>20.74630230362064</v>
       </c>
       <c r="L16" t="n">
-        <v>43.38749058688493</v>
+        <v>42.15306650903625</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93432484630472</v>
+        <v>99.96376015778816</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.18799432221745</v>
+        <v>84.08256122439589</v>
       </c>
       <c r="C17" t="n">
-        <v>38.26887433032927</v>
+        <v>40.30061891612961</v>
       </c>
       <c r="D17" t="n">
-        <v>1.383901027052966</v>
+        <v>1.483141944305909</v>
       </c>
       <c r="E17" t="n">
-        <v>12.5555312302529</v>
+        <v>12.24626450855135</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574083544692576</v>
+        <v>0.7497815689175371</v>
       </c>
       <c r="G17" t="n">
-        <v>23.60238899127513</v>
+        <v>25.8397307111987</v>
       </c>
       <c r="H17" t="n">
-        <v>37.19919111586589</v>
+        <v>37.93209440552884</v>
       </c>
       <c r="I17" t="n">
-        <v>1.955771387868441</v>
+        <v>1.145413280158929</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73380221543286</v>
+        <v>4.686134805734608</v>
       </c>
       <c r="K17" t="n">
-        <v>17.81200567778256</v>
+        <v>15.91743877560411</v>
       </c>
       <c r="L17" t="n">
-        <v>43.85397928258674</v>
+        <v>43.74377919480675</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93485929069857</v>
+        <v>99.96183688654047</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.76144779153877</v>
+        <v>85.81204725010525</v>
       </c>
       <c r="C18" t="n">
-        <v>36.1443179873533</v>
+        <v>41.00327711162278</v>
       </c>
       <c r="D18" t="n">
-        <v>1.295333720101004</v>
+        <v>1.484364255819183</v>
       </c>
       <c r="E18" t="n">
-        <v>12.02381868829596</v>
+        <v>12.83084010223783</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579245907901426</v>
+        <v>0.7503994913272208</v>
       </c>
       <c r="G18" t="n">
-        <v>22.09187632474334</v>
+        <v>25.9714655623538</v>
       </c>
       <c r="H18" t="n">
-        <v>37.22454543556442</v>
+        <v>37.96335563166601</v>
       </c>
       <c r="I18" t="n">
-        <v>1.630920339605504</v>
+        <v>2.121625385906071</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737028692438392</v>
+        <v>4.689996820795131</v>
       </c>
       <c r="K18" t="n">
-        <v>20.23855220846123</v>
+        <v>14.18795274989476</v>
       </c>
       <c r="L18" t="n">
-        <v>43.56280282118912</v>
+        <v>44.738107527927</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94567301700366</v>
+        <v>99.92933738944454</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.76339325792441</v>
+        <v>83.29991195457035</v>
       </c>
       <c r="C19" t="n">
-        <v>35.3974155041502</v>
+        <v>38.81960430869008</v>
       </c>
       <c r="D19" t="n">
-        <v>1.259549404536882</v>
+        <v>1.392789900215123</v>
       </c>
       <c r="E19" t="n">
-        <v>11.91830107665939</v>
+        <v>12.33415046851122</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583607868102057</v>
+        <v>0.7509307689937913</v>
       </c>
       <c r="G19" t="n">
-        <v>21.48157593532204</v>
+        <v>24.36921718319633</v>
       </c>
       <c r="H19" t="n">
-        <v>37.24596867313311</v>
+        <v>37.99023342573209</v>
       </c>
       <c r="I19" t="n">
-        <v>1.359882463898988</v>
+        <v>1.76927290171059</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739754917563785</v>
+        <v>4.693317306211197</v>
       </c>
       <c r="K19" t="n">
-        <v>21.23660674207558</v>
+        <v>16.70008804542967</v>
       </c>
       <c r="L19" t="n">
-        <v>43.3206744110074</v>
+        <v>44.42137360738287</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95469665723319</v>
+        <v>99.94106596150262</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.17857917984412</v>
+        <v>80.69615014579806</v>
       </c>
       <c r="C20" t="n">
-        <v>33.02184568967863</v>
+        <v>36.48905885960401</v>
       </c>
       <c r="D20" t="n">
-        <v>1.166193611207169</v>
+        <v>1.298387511034027</v>
       </c>
       <c r="E20" t="n">
-        <v>11.22390187305867</v>
+        <v>11.74403190803614</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587370201510402</v>
+        <v>0.751388387931217</v>
       </c>
       <c r="G20" t="n">
-        <v>19.88939578249045</v>
+        <v>22.71748756897998</v>
       </c>
       <c r="H20" t="n">
-        <v>37.2644469165632</v>
+        <v>38.01338476134207</v>
       </c>
       <c r="I20" t="n">
-        <v>1.133797600429595</v>
+        <v>1.475292583904516</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742106375944001</v>
+        <v>4.696177424570108</v>
       </c>
       <c r="K20" t="n">
-        <v>23.82142082015588</v>
+        <v>19.30384985420193</v>
       </c>
       <c r="L20" t="n">
-        <v>43.11895897727939</v>
+        <v>44.15794481670211</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9622254871139</v>
+        <v>99.95085353050806</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.17866771902708</v>
+        <v>78.11968092320389</v>
       </c>
       <c r="C21" t="n">
-        <v>36.80144596342874</v>
+        <v>34.13972790115169</v>
       </c>
       <c r="D21" t="n">
-        <v>1.166935527646295</v>
+        <v>1.205472227162742</v>
       </c>
       <c r="E21" t="n">
-        <v>13.24455062167154</v>
+        <v>11.10861409430817</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592197182749313</v>
+        <v>0.751782761282223</v>
       </c>
       <c r="G21" t="n">
-        <v>21.65415267285706</v>
+        <v>21.09177737970595</v>
       </c>
       <c r="H21" t="n">
-        <v>39.04025757702694</v>
+        <v>38.03333644834203</v>
       </c>
       <c r="I21" t="n">
-        <v>1.568428362331996</v>
+        <v>1.230055754388869</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745123239218321</v>
+        <v>4.698642258013895</v>
       </c>
       <c r="K21" t="n">
-        <v>17.82133228097291</v>
+        <v>21.88031907679613</v>
       </c>
       <c r="L21" t="n">
-        <v>45.32497404946396</v>
+        <v>43.93897267249928</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94775229386562</v>
+        <v>99.95901965044709</v>
       </c>
     </row>
   </sheetData>
